--- a/data/dict/expredict_public.xlsx
+++ b/data/dict/expredict_public.xlsx
@@ -5,21 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/Library/Mobile Documents/com~apple~CloudDocs/DeskTop/coding_main/kmwe_coding/data/dict/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/Library/Mobile Documents/com~apple~CloudDocs/DeskTop/Intellectual/thesis/표현문형 자동 주석 성능 향상/git/data/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5D782E-BB2B-2442-8755-8984B3E366FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12A8279-6F4A-8641-A966-0D8708B43097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="expredict" sheetId="1" r:id="rId1"/>
     <sheet name="components" sheetId="2" r:id="rId2"/>
     <sheet name="rules" sheetId="3" r:id="rId3"/>
+    <sheet name="llm_examples" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">components!$A$1:$A$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">expredict!$A$1:$A$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">llm_examples!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">rules!$A$1:$M$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="175">
   <si>
     <t>e_id</t>
   </si>
@@ -545,6 +547,39 @@
   <si>
     <t>ㄴ/은/는데2(연결어미, 대립되는 사실)</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>example_id</t>
+  </si>
+  <si>
+    <t>instance_id</t>
+  </si>
+  <si>
+    <t>example_role</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>span_segments</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>span_text</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>llm_marked_text</t>
+  </si>
+  <si>
+    <t>is_valid</t>
+  </si>
+  <si>
+    <t>validation_notes</t>
   </si>
 </sst>
 </file>
@@ -626,7 +661,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -669,6 +704,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2935,4 +2979,66 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE1218D5-08CB-CB4D-9392-A51135A35EB3}">
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="4" max="4" width="15.42578125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="54" style="17" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" style="8" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="69.85546875" style="5" customWidth="1"/>
+    <col min="9" max="9" width="20.5703125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="60.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="19" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>